--- a/change_plans.xlsx
+++ b/change_plans.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mepdw\Git\BristolFE-v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mepdw\Git\BristolFE-v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A9EACC-4159-48B1-8527-ABE906A1B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD4C99F-7446-4C51-A524-72FD89D60178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="104">
   <si>
     <t>fn_ABAQUS.m</t>
   </si>
@@ -257,9 +257,6 @@
     <t>Should make it so that general 3d bdry can be specified rather than just a cuboid (to provide same functionality as 2d versions)</t>
   </si>
   <si>
-    <t>Generalise to 3D as well, based on facet surface</t>
-  </si>
-  <si>
     <t>Tidy up. Remove options to call obsolete versions</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
     <t>Finish it! But in general, should be in code/internal functions.</t>
   </si>
   <si>
-    <t>code/code/internal/abaqus</t>
-  </si>
-  <si>
     <t>Need generalising for 3D - used in subdomain stuff</t>
   </si>
   <si>
@@ -326,12 +320,6 @@
     <t>Put all non-essential functions into code\internal if not required for general use</t>
   </si>
   <si>
-    <t>Todo</t>
-  </si>
-  <si>
-    <t>Generalise 2D one. Shouldn't be hard as key functions for getting distance to surface already done</t>
-  </si>
-  <si>
     <t>fn_3d_create_smooth_random_blob.m</t>
   </si>
   <si>
@@ -339,13 +327,34 @@
   </si>
   <si>
     <t>fn_2d_random_walk</t>
+  </si>
+  <si>
+    <t>code/internal/abaqus</t>
+  </si>
+  <si>
+    <t>Generalise 2D one, based on facet surface description</t>
+  </si>
+  <si>
+    <t>Needs facet surface description, then use internal function for getting distance to surface</t>
+  </si>
+  <si>
+    <t>Part done</t>
+  </si>
+  <si>
+    <t>Done - minor issue re-subdomains</t>
+  </si>
+  <si>
+    <t>Should work for 2d and 3d but latter needs checking</t>
+  </si>
+  <si>
+    <t>Done - needs checking in 3d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,12 +369,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -388,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -397,9 +400,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,14 +445,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:F62" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A10:F62" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="code"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:F61" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A10:F61" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:F61">
     <sortCondition ref="A10:A61"/>
   </sortState>
@@ -785,44 +779,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E84AA5C-B324-48B5-AC26-CDBD29B21C26}">
-  <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="1" customWidth="1"/>
-    <col min="6" max="6" width="78.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="44.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="78.7265625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -842,9 +836,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>44</v>
@@ -853,60 +847,57 @@
         <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>96</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>44</v>
@@ -915,29 +906,26 @@
         <v>37</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>44</v>
@@ -946,353 +934,383 @@
         <v>37</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="1" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>44</v>
@@ -1301,98 +1319,104 @@
         <v>40</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>44</v>
@@ -1401,109 +1425,79 @@
         <v>40</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>31</v>
       </c>
@@ -1514,13 +1508,13 @@
         <v>37</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>32</v>
       </c>
@@ -1531,13 +1525,13 @@
         <v>37</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>33</v>
       </c>
@@ -1548,13 +1542,13 @@
         <v>40</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>34</v>
       </c>
@@ -1565,21 +1559,7 @@
         <v>40</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/change_plans.xlsx
+++ b/change_plans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mepdw\Git\BristolFE-v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BFD9A8-EE53-4A7C-A72C-6C54B50C6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FE084A-2379-4A91-86C4-7D904EC3C923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
+    <workbookView xWindow="465" yWindow="1545" windowWidth="21600" windowHeight="11295" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="123">
   <si>
     <t>fn_ABAQUS.m</t>
   </si>
@@ -329,9 +329,6 @@
     <t>New function code written</t>
   </si>
   <si>
-    <t>New function checked</t>
-  </si>
-  <si>
     <t>New function name</t>
   </si>
   <si>
@@ -381,6 +378,33 @@
   </si>
   <si>
     <t>New function help written</t>
+  </si>
+  <si>
+    <t>fn_matl_isotropic_solid_defined_by_velocities</t>
+  </si>
+  <si>
+    <t>fn_matl_isotropic_solid_defined_by_stiffness</t>
+  </si>
+  <si>
+    <t>fn_matl_fluid_defined_by_velocity</t>
+  </si>
+  <si>
+    <t>fn_matl_fluid_defined_by_stiffness</t>
+  </si>
+  <si>
+    <t>Tested</t>
+  </si>
+  <si>
+    <t>test_2d_defects</t>
+  </si>
+  <si>
+    <t>Test script (in /tests)</t>
+  </si>
+  <si>
+    <t>test_2d_meshing_functions</t>
+  </si>
+  <si>
+    <t>multiple places</t>
   </si>
 </sst>
 </file>
@@ -460,22 +484,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -487,6 +496,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -506,6 +518,21 @@
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -520,21 +547,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:I62" totalsRowShown="0" headerRowDxfId="0" dataDxfId="10">
-  <autoFilter ref="A10:I62" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:J66" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A10:J66" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:J61">
     <sortCondition ref="A10:A61"/>
   </sortState>
-  <tableColumns count="9">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5BB31C36-8D73-477E-A058-A36FBB13E609}" name="Old function name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{EEF3EC8B-5ACF-41CA-BB14-DD6FFB50701A}" name="New function name" dataDxfId="8"/>
     <tableColumn id="7" xr3:uid="{36E6CD37-A715-4A09-BA94-09B4F98158A8}" name="New function file exists" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{F52BA5B1-610C-4D51-9B39-CA1F0158C033}" name="New function code written" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{851E8FFF-BA01-46C6-A6E6-3618FB90F659}" name="New function help written" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{7E07841A-BEC1-42B3-BF82-FF19FDAA1062}" name="New function checked" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{070E5D9D-710E-4450-AAC5-623CC7A95867}" name="2D/3D/Both" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9FA61B46-BBE2-498C-8D92-E0AF967CB5B6}" name="New function location" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{18FFD21B-9EA6-4CD5-9AEF-2635DF47807A}" name="Action" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{851E8FFF-BA01-46C6-A6E6-3618FB90F659}" name="New function help written" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{7E07841A-BEC1-42B3-BF82-FF19FDAA1062}" name="Tested" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{315FBA42-E8A4-4A1B-A610-C990F73976FE}" name="Test script (in /tests)" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{070E5D9D-710E-4450-AAC5-623CC7A95867}" name="2D/3D/Both" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{9FA61B46-BBE2-498C-8D92-E0AF967CB5B6}" name="New function location" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{18FFD21B-9EA6-4CD5-9AEF-2635DF47807A}" name="Action" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -857,50 +885,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E84AA5C-B324-48B5-AC26-CDBD29B21C26}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
     <col min="4" max="6" width="9.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="78.7109375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="1"/>
+    <col min="7" max="7" width="22.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="78.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="5" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>95</v>
@@ -909,146 +938,194 @@
         <v>96</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="I10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="B15" t="s">
         <v>89</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I16" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>94</v>
       </c>
@@ -1056,176 +1133,161 @@
         <v>62</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I17" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -1233,25 +1295,31 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>2</v>
       </c>
@@ -1259,19 +1327,25 @@
         <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1279,19 +1353,19 @@
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1299,22 +1373,22 @@
         <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -1322,171 +1396,171 @@
         <v>5</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I34" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="J38" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>54</v>
@@ -1494,292 +1568,348 @@
       <c r="D40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="J44" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="J46" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="J47" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I48" s="2" t="s">
+      <c r="I48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J51" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="J52" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="J54" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="J55" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I58" s="2" t="s">
+      <c r="I58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I60" s="2" t="s">
+      <c r="I60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I61" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>108</v>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/change_plans.xlsx
+++ b/change_plans.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mepdw\Git\BristolFE-v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FE084A-2379-4A91-86C4-7D904EC3C923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D7F65F-58BA-4F2D-BE71-E70E36F87A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="465" yWindow="1545" windowWidth="21600" windowHeight="11295" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="133">
   <si>
     <t>fn_ABAQUS.m</t>
   </si>
@@ -167,9 +168,6 @@
     <t>Done</t>
   </si>
   <si>
-    <t>Generalise</t>
-  </si>
-  <si>
     <t>Should work in 3D - needs checking</t>
   </si>
   <si>
@@ -209,18 +207,12 @@
     <t>General principles</t>
   </si>
   <si>
-    <t>Public functions for 2d/3d should be same if arguments exactly the same but not otherwise (rather than using same function with dummary argument, even if that happens behind the scenes)</t>
-  </si>
-  <si>
     <t>Public functions should be fully documented in header comments</t>
   </si>
   <si>
     <t>Make sure all examples only use public functions</t>
   </si>
   <si>
-    <t>Update</t>
-  </si>
-  <si>
     <t>fn_3d_tetrahedral_structured_mesh.m</t>
   </si>
   <si>
@@ -405,6 +397,45 @@
   </si>
   <si>
     <t>multiple places</t>
+  </si>
+  <si>
+    <t>Works for 2D, needs generalisation to 3D</t>
+  </si>
+  <si>
+    <t>fn_estimate_max_min_wavelengths</t>
+  </si>
+  <si>
+    <t>fn_hann_pulse</t>
+  </si>
+  <si>
+    <t>test_3d_defects</t>
+  </si>
+  <si>
+    <t>test_3d_meshing_functions</t>
+  </si>
+  <si>
+    <t>fn_2d_create_subdomain</t>
+  </si>
+  <si>
+    <t>ex_2d_subdomain in examples</t>
+  </si>
+  <si>
+    <t>test_matls</t>
+  </si>
+  <si>
+    <t>Public functions for 2d/3d should be same if arguments exactly the same but not otherwise (rather than using same function with dummy argument, even if that happens behind the scenes)</t>
+  </si>
+  <si>
+    <t>fn_matl_fluid_defined_by_bulk_modulus</t>
+  </si>
+  <si>
+    <t>test_signals</t>
+  </si>
+  <si>
+    <t>subdomains</t>
+  </si>
+  <si>
+    <t>fn_3d_spherical_surface</t>
   </si>
 </sst>
 </file>
@@ -486,9 +517,6 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -496,6 +524,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -547,8 +578,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:J66" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A10:J66" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:J74" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A10:J74" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="code"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:J61">
     <sortCondition ref="A10:A61"/>
   </sortState>
@@ -559,10 +596,10 @@
     <tableColumn id="3" xr3:uid="{F52BA5B1-610C-4D51-9B39-CA1F0158C033}" name="New function code written" dataDxfId="6"/>
     <tableColumn id="9" xr3:uid="{851E8FFF-BA01-46C6-A6E6-3618FB90F659}" name="New function help written" dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{7E07841A-BEC1-42B3-BF82-FF19FDAA1062}" name="Tested" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{315FBA42-E8A4-4A1B-A610-C990F73976FE}" name="Test script (in /tests)" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{070E5D9D-710E-4450-AAC5-623CC7A95867}" name="2D/3D/Both" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9FA61B46-BBE2-498C-8D92-E0AF967CB5B6}" name="New function location" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{18FFD21B-9EA6-4CD5-9AEF-2635DF47807A}" name="Action" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{315FBA42-E8A4-4A1B-A610-C990F73976FE}" name="Test script (in /tests)" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{070E5D9D-710E-4450-AAC5-623CC7A95867}" name="2D/3D/Both" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9FA61B46-BBE2-498C-8D92-E0AF967CB5B6}" name="New function location" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{18FFD21B-9EA6-4CD5-9AEF-2635DF47807A}" name="Action" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -885,13 +922,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E84AA5C-B324-48B5-AC26-CDBD29B21C26}">
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
-    <col min="4" max="6" width="9.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="6" width="9.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="25" style="1" customWidth="1"/>
@@ -901,56 +939,56 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="5" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>39</v>
@@ -958,333 +996,360 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>104</v>
+      <c r="E23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1295,31 +1360,31 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>2</v>
       </c>
@@ -1327,25 +1392,25 @@
         <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1353,19 +1418,19 @@
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1373,22 +1438,22 @@
         <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -1396,42 +1461,42 @@
         <v>5</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1439,27 +1504,36 @@
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1467,19 +1541,25 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1487,33 +1567,33 @@
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
@@ -1521,13 +1601,13 @@
         <v>36</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>12</v>
       </c>
@@ -1535,24 +1615,24 @@
         <v>36</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>40</v>
@@ -1560,63 +1640,75 @@
     </row>
     <row r="40" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="C43" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="D43" s="1" t="s">
-        <v>42</v>
+        <v>99</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -1630,29 +1722,29 @@
         <v>38</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -1666,7 +1758,7 @@
         <v>38</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>40</v>
@@ -1683,13 +1775,13 @@
         <v>38</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>23</v>
       </c>
@@ -1697,10 +1789,10 @@
         <v>42</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>24</v>
       </c>
@@ -1711,29 +1803,29 @@
         <v>38</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>27</v>
       </c>
@@ -1741,18 +1833,18 @@
         <v>42</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -1760,19 +1852,19 @@
         <v>29</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
@@ -1780,7 +1872,7 @@
         <v>42</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -1788,13 +1880,16 @@
         <v>31</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>41</v>
@@ -1805,13 +1900,13 @@
         <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>41</v>
@@ -1828,10 +1923,10 @@
         <v>38</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -1845,71 +1940,276 @@
         <v>38</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="C66" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/change_plans.xlsx
+++ b/change_plans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mepdw\Git\BristolFE-v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D7F65F-58BA-4F2D-BE71-E70E36F87A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D5A4BB-B66A-487E-BFC8-B62B85FA928D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ED4B7BA-7B1F-440F-83D9-1CC24D319783}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="138">
   <si>
     <t>fn_ABAQUS.m</t>
   </si>
@@ -436,6 +435,21 @@
   </si>
   <si>
     <t>fn_3d_spherical_surface</t>
+  </si>
+  <si>
+    <t>fn_3d_signed_dist_to_bdry</t>
+  </si>
+  <si>
+    <t>fn_2d_signed_dist_to_bdry</t>
+  </si>
+  <si>
+    <t>test_2d_signed_distance_to_boundary</t>
+  </si>
+  <si>
+    <t>test_3d_signed_distance_to_boundary</t>
+  </si>
+  <si>
+    <t>fn_3d_elements_in_region.m</t>
   </si>
 </sst>
 </file>
@@ -578,14 +592,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:J74" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A10:J74" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="code"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}" name="Table1" displayName="Table1" ref="A10:J77" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A10:J77" xr:uid="{9F00509C-FE5D-4C03-9CC3-9ADEE36D4BF5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:J61">
     <sortCondition ref="A10:A61"/>
   </sortState>
@@ -922,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E84AA5C-B324-48B5-AC26-CDBD29B21C26}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1335,7 +1343,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1384,7 +1392,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>2</v>
       </c>
@@ -1410,7 +1418,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1430,7 +1438,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1453,7 +1461,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -1476,7 +1484,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -1512,12 +1520,18 @@
       <c r="D32" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="E32" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="F32" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>118</v>
       </c>
+      <c r="H32" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="I32" s="1" t="s">
         <v>70</v>
       </c>
@@ -1525,7 +1539,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>8</v>
       </c>
@@ -1585,7 +1599,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
@@ -1593,7 +1607,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
@@ -1607,7 +1621,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>12</v>
       </c>
@@ -1658,7 +1672,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>14</v>
       </c>
@@ -1666,7 +1680,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1703,7 +1717,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
@@ -1728,7 +1742,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
@@ -1739,7 +1753,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>20</v>
       </c>
@@ -1781,7 +1795,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>23</v>
       </c>
@@ -1792,7 +1806,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>24</v>
       </c>
@@ -1809,7 +1823,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>25</v>
       </c>
@@ -1817,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>26</v>
       </c>
@@ -1825,7 +1839,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>27</v>
       </c>
@@ -1839,7 +1853,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>28</v>
       </c>
@@ -1864,7 +1878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
@@ -1933,17 +1947,11 @@
       <c r="B61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J61" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>103</v>
       </c>
@@ -1951,7 +1959,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>111</v>
       </c>
@@ -1965,7 +1973,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>112</v>
       </c>
@@ -1979,7 +1987,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>113</v>
       </c>
@@ -1993,7 +2001,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>114</v>
       </c>
@@ -2209,6 +2217,84 @@
         <v>37</v>
       </c>
       <c r="I74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>70</v>
       </c>
     </row>
